--- a/artfynd/A 27591-2024 artfynd.xlsx
+++ b/artfynd/A 27591-2024 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114939983</v>
+        <v>121667640</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -721,7 +721,7 @@
         <v>6648182</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Esplund, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 27591-2024 artfynd.xlsx
+++ b/artfynd/A 27591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667640</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 27591-2024 artfynd.xlsx
+++ b/artfynd/A 27591-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>121667640</v>
       </c>
       <c r="B2" t="n">
-        <v>57381</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 27591-2024 artfynd.xlsx
+++ b/artfynd/A 27591-2024 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 27591-2024 artfynd.xlsx
+++ b/artfynd/A 27591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667640</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
+          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 27591-2024 artfynd.xlsx
+++ b/artfynd/A 27591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667640</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 27591-2024 artfynd.xlsx
+++ b/artfynd/A 27591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667640</v>
       </c>
       <c r="B2" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 27591-2024 artfynd.xlsx
+++ b/artfynd/A 27591-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121667640</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Berg, Enviro Planning, Anders Esplund, Pia Edfors</t>
+          <t>Pia Edfors, Anders Esplund, Enviro Planning, Sofia Berg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
